--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_chara.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_chara.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="138">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -265,6 +265,42 @@
     <t xml:space="preserve">(#self is too pumped up at the party.)</t>
   </si>
   <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#selfはあなた達二人に乾杯した！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self raises a toast to the two of you!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#selfは幸せそうにあなたに微笑んだ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self smiles at you happily.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_hater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(プンスコ！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Pouting in a huff.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_cutter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…あなた（ポッ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...My love. (blushing)</t>
+  </si>
+  <si>
     <t xml:space="preserve">encounter_mob</t>
   </si>
   <si>
@@ -368,6 +404,18 @@
   </si>
   <si>
     <t xml:space="preserve">(#self在派对上太兴奋了。)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self为你们二人干杯！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self一脸幸福地对你微笑)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(哼！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…亲爱的（脸红）</t>
   </si>
   <si>
     <t xml:space="preserve">不想死的话就把#1交出来{。}！</t>
@@ -697,7 +745,7 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
     <col min="1" max="1" width="21.14" style="1" customWidth="1"/>
@@ -748,7 +796,7 @@
     <row r="2" ht="12.8">
       <c r="H2" s="1">
         <f>MAX(H4:H1048576)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="12.8">
@@ -847,7 +895,7 @@
         <v>24</v>
       </c>
       <c r="K25" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" ht="12.8">
@@ -941,7 +989,7 @@
         <v>33</v>
       </c>
       <c r="K39" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" ht="12.8">
@@ -964,7 +1012,7 @@
         <v>37</v>
       </c>
       <c r="K40" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" ht="12.8">
@@ -984,7 +1032,7 @@
         <v>40</v>
       </c>
       <c r="K41" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" ht="12.8">
@@ -1078,7 +1126,7 @@
         <v>49</v>
       </c>
       <c r="K61" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" ht="12.8">
@@ -1110,7 +1158,7 @@
         <v>54</v>
       </c>
       <c r="K66" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="67" ht="12.8">
@@ -1134,7 +1182,7 @@
         <v>57</v>
       </c>
       <c r="K70" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="71" ht="12.8">
@@ -1158,7 +1206,7 @@
         <v>60</v>
       </c>
       <c r="K74" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
     </row>
     <row r="75" ht="12.8">
@@ -1182,7 +1230,7 @@
         <v>63</v>
       </c>
       <c r="K79" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
     </row>
     <row r="80" ht="12.8">
@@ -1196,7 +1244,7 @@
         <v>65</v>
       </c>
       <c r="K80" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
     </row>
     <row r="81" ht="12.8">
@@ -1225,7 +1273,7 @@
         <v>68</v>
       </c>
       <c r="K85" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
     </row>
     <row r="86" ht="12.8">
@@ -1254,7 +1302,7 @@
         <v>71</v>
       </c>
       <c r="K91" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" ht="12.8">
@@ -1278,7 +1326,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
     </row>
     <row r="96" ht="12.8">
@@ -1302,7 +1350,7 @@
         <v>77</v>
       </c>
       <c r="K100" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="101" ht="12.8">
@@ -1326,7 +1374,7 @@
         <v>80</v>
       </c>
       <c r="K104" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="105" ht="12.8">
@@ -1334,166 +1382,262 @@
         <v>25</v>
       </c>
     </row>
+    <row r="107" ht="12.8">
+      <c r="A107" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="108" ht="12.8">
-      <c r="A108" s="1" t="s">
-        <v>81</v>
+      <c r="H108" s="1">
+        <v>22</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K108" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="109" ht="12.8">
-      <c r="H109" s="1">
-        <v>16</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K109" t="s">
-        <v>116</v>
+      <c r="B109" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="110" ht="12.8">
-      <c r="J110" s="4"/>
+      <c r="A110" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="111" ht="12.8">
-      <c r="B111" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="H111" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J111" s="1" t="s">
+      <c r="J111" s="4" t="s">
         <v>86</v>
       </c>
       <c r="K111" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112" ht="12.8">
       <c r="B112" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" ht="12.8">
+      <c r="A113" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D112" s="1" t="s">
+    </row>
+    <row r="114" ht="12.8">
+      <c r="H114" s="1">
+        <v>24</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K114" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" ht="12.8">
+      <c r="B115" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" ht="12.8">
+      <c r="A116" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="117" ht="12.8">
+      <c r="H117" s="1">
+        <v>25</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K117" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="118" ht="12.8">
+      <c r="B118" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" ht="12.8">
+      <c r="A120" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" ht="12.8">
+      <c r="H121" s="1">
+        <v>16</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J121" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="K121" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="122" ht="12.8">
+      <c r="J122" s="4"/>
+    </row>
+    <row r="123" ht="12.8">
+      <c r="B123" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H112" s="1">
+      <c r="H123" s="1">
+        <v>17</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K123" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" ht="12.8">
+      <c r="B124" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H124" s="1">
         <v>18</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K112" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="113" ht="12.8">
-      <c r="J113" s="4"/>
-    </row>
-    <row r="114" ht="12.8">
-      <c r="J114" s="4"/>
-    </row>
-    <row r="115" ht="12.8">
-      <c r="J115" s="4"/>
-    </row>
-    <row r="117" ht="12.8">
-      <c r="A117" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="119" ht="12.8">
-      <c r="D119" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="120" ht="12.8">
-      <c r="B120" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="122" ht="12.8">
-      <c r="A122" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="123" ht="12.8">
-      <c r="H123" s="1">
+      <c r="I124" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K124" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="125" ht="12.8">
+      <c r="J125" s="4"/>
+    </row>
+    <row r="126" ht="12.8">
+      <c r="J126" s="4"/>
+    </row>
+    <row r="127" ht="12.8">
+      <c r="J127" s="4"/>
+    </row>
+    <row r="129" ht="12.8">
+      <c r="A129" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="131" ht="12.8">
+      <c r="D131" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="132" ht="12.8">
+      <c r="B132" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" ht="12.8">
+      <c r="A134" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="135" ht="12.8">
+      <c r="H135" s="1">
         <v>19</v>
       </c>
-      <c r="I123" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="K123" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="124" ht="12.8">
-      <c r="D124" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="126" ht="12.8">
-      <c r="B126" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="128" ht="12.8">
-      <c r="A128" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="129" ht="12.8">
-      <c r="H129" s="1">
+      <c r="I135" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" ht="12.8">
+      <c r="D136" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="138" ht="12.8">
+      <c r="B138" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" ht="12.8">
+      <c r="A140" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="141" ht="12.8">
+      <c r="H141" s="1">
         <v>20</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J129" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="K129" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="130" ht="12.8">
-      <c r="B130" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="132" ht="12.8">
-      <c r="A132" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="133" ht="12.8">
-      <c r="H133" s="1">
+      <c r="I141" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="K141" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142" ht="12.8">
+      <c r="B142" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" ht="12.8">
+      <c r="A144" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="145" ht="12.8">
+      <c r="H145" s="1">
         <v>21</v>
       </c>
-      <c r="I133" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J133" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K133" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="134" ht="12.8">
-      <c r="B134" s="1" t="s">
+      <c r="I145" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="K145" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="146" ht="12.8">
+      <c r="B146" s="1" t="s">
         <v>25</v>
       </c>
     </row>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_chara.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_chara.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="chara" sheetId="1" r:id="rId3"/>
+    <sheet name="chara" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="112">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -356,84 +356,6 @@
   </si>
   <si>
     <t xml:space="preserve">I made this... care to try?</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">(你在自言自语)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">招纳 (#2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">招纳 #1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">再考虑考虑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接待#1。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#self睡着了)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">救救我{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#self用惊疑的眼神盯着空气)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我认输{。}！是你赢了{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这个给你当胜利的纪念品。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">到此为止{。}。只有嘴上功夫的家伙{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没想到你能活着回来{。}！好了，请收下约定好的报酬{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看来对你来说负担太大了{。}。真遗憾{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请把我安全地护送到目的地{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#self在派对上太兴奋了。)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#self为你们二人干杯！)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(#self一脸幸福地对你微笑)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(哼！)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…亲爱的（脸红）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不想死的话就把#1交出来{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奋起反击</t>
-  </si>
-  <si>
-    <t xml:space="preserve">投降 (失去: #2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明智的选择{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">请收下这个{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{我}试着做了这个{。}，请尝尝看吧{。}。</t>
   </si>
 </sst>
 </file>
@@ -454,19 +376,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -504,7 +426,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -513,54 +435,54 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -741,24 +663,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L146"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="21.14" style="1" customWidth="1"/>
-    <col min="2" max="3" width="8.84" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.84" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.84" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.13" style="1" customWidth="1"/>
-    <col min="10" max="10" width="53.27" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.27"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,28 +715,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="12.8">
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" ht="12.8">
+    <row r="11" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -830,12 +752,12 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I13" s="1" t="s">
         <v>16</v>
       </c>
@@ -843,32 +765,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" ht="12.8">
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" ht="12.8">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="3" customFormat="1" ht="12.8">
+    <row r="24" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -884,8 +806,8 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" ht="12.8">
-      <c r="H25" s="1">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H25" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -894,11 +816,8 @@
       <c r="J25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" ht="12.8">
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
@@ -906,12 +825,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" ht="12.8">
+    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
@@ -927,7 +846,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" ht="12.8">
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I30" s="1" t="s">
         <v>16</v>
       </c>
@@ -935,17 +854,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" s="3" customFormat="1" ht="12.8">
+    <row r="35" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>27</v>
       </c>
@@ -961,7 +880,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="37" ht="12.8">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I37" s="1" t="s">
         <v>28</v>
       </c>
@@ -969,7 +888,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" ht="12.8">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
         <v>29</v>
       </c>
@@ -979,7 +898,7 @@
       <c r="D39" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -988,11 +907,8 @@
       <c r="J39" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K39" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" ht="12.8">
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
         <v>34</v>
       </c>
@@ -1002,7 +918,7 @@
       <c r="D40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -1011,18 +927,15 @@
       <c r="J40" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K40" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" ht="12.8">
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -1031,21 +944,18 @@
       <c r="J41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K41" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" ht="12.8">
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" ht="12.8">
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I45" s="1" t="s">
         <v>41</v>
       </c>
@@ -1053,7 +963,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="1" t="s">
         <v>42</v>
       </c>
@@ -1061,17 +971,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="49" ht="12.8">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I49" s="1" t="s">
         <v>41</v>
       </c>
@@ -1079,7 +989,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" ht="12.8">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="1" t="s">
         <v>42</v>
       </c>
@@ -1087,27 +997,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" ht="12.8">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="54" ht="12.8">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="55" ht="12.8">
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D60" s="1" t="s">
         <v>46</v>
       </c>
@@ -1115,8 +1025,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" ht="12.8">
-      <c r="H61" s="1">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H61" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -1125,11 +1035,8 @@
       <c r="J61" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K61" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="62" ht="12.8">
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D62" s="1" t="s">
         <v>50</v>
       </c>
@@ -1137,18 +1044,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="63" ht="12.8">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="65" ht="12.8">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="66" ht="12.8">
-      <c r="H66" s="1">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -1157,22 +1064,19 @@
       <c r="J66" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K66" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="67" ht="12.8">
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="69" ht="12.8">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="70" ht="12.8">
-      <c r="H70" s="1">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H70" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -1181,22 +1085,19 @@
       <c r="J70" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K70" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" ht="12.8">
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="73" ht="12.8">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="74" ht="12.8">
-      <c r="H74" s="1">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -1205,22 +1106,19 @@
       <c r="J74" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K74" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="75" ht="12.8">
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="78" ht="12.8">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="79" ht="12.8">
-      <c r="H79" s="1">
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H79" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -1229,12 +1127,9 @@
       <c r="J79" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K79" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="80" ht="12.8">
-      <c r="H80" s="1">
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -1243,27 +1138,24 @@
       <c r="J80" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="K80" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="81" ht="12.8">
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D81" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="82" ht="12.8">
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="84" ht="12.8">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="85" ht="12.8">
-      <c r="H85" s="1">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -1272,27 +1164,24 @@
       <c r="J85" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="K85" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="86" ht="12.8">
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D86" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" ht="12.8">
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="90" ht="12.8">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="91" ht="12.8">
-      <c r="H91" s="1">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -1301,22 +1190,19 @@
       <c r="J91" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="K91" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="92" ht="12.8">
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="94" ht="12.8">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="95" ht="12.8">
-      <c r="H95" s="1">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H95" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -1325,22 +1211,19 @@
       <c r="J95" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="K95" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="96" ht="12.8">
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="99" ht="12.8">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="100" ht="12.8">
-      <c r="H100" s="1">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H100" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I100" s="1" t="s">
@@ -1349,22 +1232,19 @@
       <c r="J100" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K100" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="101" ht="12.8">
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="103" ht="12.8">
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="104" ht="12.8">
-      <c r="H104" s="1">
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H104" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I104" s="1" t="s">
@@ -1373,22 +1253,19 @@
       <c r="J104" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="K104" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="105" ht="12.8">
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="107" ht="12.8">
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="108" ht="12.8">
-      <c r="H108" s="1">
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H108" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -1397,22 +1274,19 @@
       <c r="J108" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="K108" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="109" ht="12.8">
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="110" ht="12.8">
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="111" ht="12.8">
-      <c r="H111" s="1">
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H111" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I111" s="1" t="s">
@@ -1421,22 +1295,19 @@
       <c r="J111" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="K111" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="112" ht="12.8">
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="113" ht="12.8">
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="114" ht="12.8">
-      <c r="H114" s="1">
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H114" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I114" s="1" t="s">
@@ -1445,22 +1316,19 @@
       <c r="J114" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="K114" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" ht="12.8">
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="116" ht="12.8">
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="117" ht="12.8">
-      <c r="H117" s="1">
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H117" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I117" s="1" t="s">
@@ -1469,22 +1337,19 @@
       <c r="J117" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="K117" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="118" ht="12.8">
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="120" ht="12.8">
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="121" ht="12.8">
-      <c r="H121" s="1">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H121" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I121" s="1" t="s">
@@ -1493,21 +1358,18 @@
       <c r="J121" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="K121" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="122" ht="12.8">
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J122" s="4"/>
     </row>
-    <row r="123" ht="12.8">
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H123" s="1">
+      <c r="H123" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -1516,18 +1378,15 @@
       <c r="J123" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K123" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="124" ht="12.8">
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H124" s="1">
+      <c r="H124" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -1536,41 +1395,38 @@
       <c r="J124" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="K124" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="125" ht="12.8">
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J125" s="4"/>
     </row>
-    <row r="126" ht="12.8">
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J126" s="4"/>
     </row>
-    <row r="127" ht="12.8">
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="J127" s="4"/>
     </row>
-    <row r="129" ht="12.8">
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="131" ht="12.8">
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="132" ht="12.8">
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="134" ht="12.8">
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="135" ht="12.8">
-      <c r="H135" s="1">
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H135" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I135" s="1" t="s">
@@ -1579,27 +1435,24 @@
       <c r="J135" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="K135" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="136" ht="12.8">
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D136" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="138" ht="12.8">
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="140" ht="12.8">
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="141" ht="12.8">
-      <c r="H141" s="1">
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H141" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I141" s="1" t="s">
@@ -1608,22 +1461,19 @@
       <c r="J141" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="K141" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="142" ht="12.8">
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="144" ht="12.8">
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="145" ht="12.8">
-      <c r="H145" s="1">
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H145" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -1632,20 +1482,17 @@
       <c r="J145" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="K145" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="146" ht="12.8">
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="1" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_chara.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/_chara.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="chara" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="chara" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="138">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -356,6 +356,84 @@
   </si>
   <si>
     <t xml:space="preserve">I made this... care to try?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(你在自言自语)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">招纳 (#2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">招纳 #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">再考虑考虑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接待#1。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self睡着了)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">救救我{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self用惊疑的眼神盯着空气)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我认输{。}！是你赢了{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这个给你当胜利的纪念品。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">到此为止{。}。只有嘴上功夫的家伙{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没想到你能活着回来{。}！好了，请收下约定好的报酬{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看来对你来说负担太大了{。}。真遗憾{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请把我安全地护送到目的地{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self在派对上太兴奋了。)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self为你们二人干杯！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self一脸幸福地对你微笑)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(哼！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…亲爱的（脸红）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不想死的话就把#1交出来{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">奋起反击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">投降 (失去: #2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明智的选择{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">请收下这个{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{我}试着做了这个{。}，请尝尝看吧{。}。</t>
   </si>
 </sst>
 </file>
@@ -376,19 +454,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -426,7 +504,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -435,54 +513,54 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -663,24 +741,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L146"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="42.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="53.27"/>
+    <col min="1" max="1" width="21.14" style="1" customWidth="1"/>
+    <col min="2" max="3" width="8.84" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.84" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.84" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="53.27" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -715,28 +793,28 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="12.8">
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" s="3" customFormat="1" ht="12.8">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -752,12 +830,12 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="I13" s="1" t="s">
         <v>16</v>
       </c>
@@ -765,32 +843,32 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" ht="12.8">
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="D17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="D18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" s="3" customFormat="1" ht="12.8">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -806,8 +884,8 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H25" s="1" t="n">
+    <row r="25" ht="12.8">
+      <c r="H25" s="1">
         <v>1</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -816,8 +894,11 @@
       <c r="J25" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K25" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" ht="12.8">
       <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
@@ -825,12 +906,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="D27" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" s="3" customFormat="1" ht="12.8">
       <c r="A29" s="1" t="s">
         <v>26</v>
       </c>
@@ -846,7 +927,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
     </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" ht="12.8">
       <c r="I30" s="1" t="s">
         <v>16</v>
       </c>
@@ -854,17 +935,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="D31" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" s="3" customFormat="1" ht="12.8">
       <c r="A35" s="1" t="s">
         <v>27</v>
       </c>
@@ -880,7 +961,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
     </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" ht="12.8">
       <c r="I37" s="1" t="s">
         <v>28</v>
       </c>
@@ -888,7 +969,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" ht="12.8">
       <c r="B39" s="1" t="s">
         <v>29</v>
       </c>
@@ -898,7 +979,7 @@
       <c r="D39" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="1" t="n">
+      <c r="H39" s="1">
         <v>15</v>
       </c>
       <c r="I39" s="1" t="s">
@@ -907,8 +988,11 @@
       <c r="J39" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" ht="12.8">
       <c r="B40" s="1" t="s">
         <v>34</v>
       </c>
@@ -918,7 +1002,7 @@
       <c r="D40" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="H40" s="1">
         <v>2</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -927,15 +1011,18 @@
       <c r="J40" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" ht="12.8">
       <c r="B41" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H41" s="1" t="n">
+      <c r="H41" s="1">
         <v>3</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -944,18 +1031,21 @@
       <c r="J41" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="D42" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" ht="12.8">
       <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" ht="12.8">
       <c r="I45" s="1" t="s">
         <v>41</v>
       </c>
@@ -963,7 +1053,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="D46" s="1" t="s">
         <v>42</v>
       </c>
@@ -971,17 +1061,17 @@
         <v>43</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="B47" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="A48" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" ht="12.8">
       <c r="I49" s="1" t="s">
         <v>41</v>
       </c>
@@ -989,7 +1079,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" ht="12.8">
       <c r="D50" s="1" t="s">
         <v>42</v>
       </c>
@@ -997,27 +1087,27 @@
         <v>44</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="12.8">
       <c r="B51" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" ht="12.8">
       <c r="A54" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" ht="12.8">
       <c r="B55" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="A59" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="D60" s="1" t="s">
         <v>46</v>
       </c>
@@ -1025,8 +1115,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H61" s="1" t="n">
+    <row r="61" ht="12.8">
+      <c r="H61" s="1">
         <v>4</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -1035,8 +1125,11 @@
       <c r="J61" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="62" ht="12.8">
       <c r="D62" s="1" t="s">
         <v>50</v>
       </c>
@@ -1044,18 +1137,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" ht="12.8">
       <c r="B63" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" ht="12.8">
       <c r="A65" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+    <row r="66" ht="12.8">
+      <c r="H66" s="1">
         <v>5</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -1064,19 +1157,22 @@
       <c r="J66" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="67" ht="12.8">
       <c r="B67" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.8">
       <c r="A69" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H70" s="1" t="n">
+    <row r="70" ht="12.8">
+      <c r="H70" s="1">
         <v>6</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -1085,19 +1181,22 @@
       <c r="J70" s="1" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K70" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" ht="12.8">
       <c r="B71" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="12.8">
       <c r="A73" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H74" s="1" t="n">
+    <row r="74" ht="12.8">
+      <c r="H74" s="1">
         <v>7</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -1106,19 +1205,22 @@
       <c r="J74" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K74" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="75" ht="12.8">
       <c r="B75" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" ht="12.8">
       <c r="A78" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H79" s="1" t="n">
+    <row r="79" ht="12.8">
+      <c r="H79" s="1">
         <v>8</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -1127,9 +1229,12 @@
       <c r="J79" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="1" t="n">
+      <c r="K79" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="80" ht="12.8">
+      <c r="H80" s="1">
         <v>10</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -1138,24 +1243,27 @@
       <c r="J80" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="81" ht="12.8">
       <c r="D81" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" ht="12.8">
       <c r="B82" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="12.8">
       <c r="A84" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H85" s="1" t="n">
+    <row r="85" ht="12.8">
+      <c r="H85" s="1">
         <v>9</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -1164,24 +1272,27 @@
       <c r="J85" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K85" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="86" ht="12.8">
       <c r="D86" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="12.8">
       <c r="B87" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" ht="12.8">
       <c r="A90" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H91" s="1" t="n">
+    <row r="91" ht="12.8">
+      <c r="H91" s="1">
         <v>11</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -1190,19 +1301,22 @@
       <c r="J91" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K91" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="92" ht="12.8">
       <c r="B92" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" ht="12.8">
       <c r="A94" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H95" s="1" t="n">
+    <row r="95" ht="12.8">
+      <c r="H95" s="1">
         <v>12</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -1211,19 +1325,22 @@
       <c r="J95" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K95" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="96" ht="12.8">
       <c r="B96" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="12.8">
       <c r="A99" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H100" s="1" t="n">
+    <row r="100" ht="12.8">
+      <c r="H100" s="1">
         <v>13</v>
       </c>
       <c r="I100" s="1" t="s">
@@ -1232,19 +1349,22 @@
       <c r="J100" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K100" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="101" ht="12.8">
       <c r="B101" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" ht="12.8">
       <c r="A103" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H104" s="1" t="n">
+    <row r="104" ht="12.8">
+      <c r="H104" s="1">
         <v>14</v>
       </c>
       <c r="I104" s="1" t="s">
@@ -1253,19 +1373,22 @@
       <c r="J104" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K104" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" ht="12.8">
       <c r="B105" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" ht="12.8">
       <c r="A107" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H108" s="1" t="n">
+    <row r="108" ht="12.8">
+      <c r="H108" s="1">
         <v>22</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -1274,19 +1397,22 @@
       <c r="J108" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K108" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="109" ht="12.8">
       <c r="B109" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" ht="12.8">
       <c r="A110" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H111" s="1" t="n">
+    <row r="111" ht="12.8">
+      <c r="H111" s="1">
         <v>23</v>
       </c>
       <c r="I111" s="1" t="s">
@@ -1295,19 +1421,22 @@
       <c r="J111" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K111" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="112" ht="12.8">
       <c r="B112" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" ht="12.8">
       <c r="A113" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H114" s="1" t="n">
+    <row r="114" ht="12.8">
+      <c r="H114" s="1">
         <v>24</v>
       </c>
       <c r="I114" s="1" t="s">
@@ -1316,19 +1445,22 @@
       <c r="J114" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K114" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="115" ht="12.8">
       <c r="B115" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" ht="12.8">
       <c r="A116" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H117" s="1" t="n">
+    <row r="117" ht="12.8">
+      <c r="H117" s="1">
         <v>25</v>
       </c>
       <c r="I117" s="1" t="s">
@@ -1337,19 +1469,22 @@
       <c r="J117" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K117" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="118" ht="12.8">
       <c r="B118" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" ht="12.8">
       <c r="A120" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H121" s="1" t="n">
+    <row r="121" ht="12.8">
+      <c r="H121" s="1">
         <v>16</v>
       </c>
       <c r="I121" s="1" t="s">
@@ -1358,18 +1493,21 @@
       <c r="J121" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K121" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="122" ht="12.8">
       <c r="J122" s="4"/>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" ht="12.8">
       <c r="B123" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H123" s="1" t="n">
+      <c r="H123" s="1">
         <v>17</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -1378,15 +1516,18 @@
       <c r="J123" s="1" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K123" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="124" ht="12.8">
       <c r="B124" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H124" s="1" t="n">
+      <c r="H124" s="1">
         <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -1395,38 +1536,41 @@
       <c r="J124" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K124" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="125" ht="12.8">
       <c r="J125" s="4"/>
     </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" ht="12.8">
       <c r="J126" s="4"/>
     </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" ht="12.8">
       <c r="J127" s="4"/>
     </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" ht="12.8">
       <c r="A129" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" ht="12.8">
       <c r="D131" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" ht="12.8">
       <c r="B132" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" ht="12.8">
       <c r="A134" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H135" s="1" t="n">
+    <row r="135" ht="12.8">
+      <c r="H135" s="1">
         <v>19</v>
       </c>
       <c r="I135" s="1" t="s">
@@ -1435,24 +1579,27 @@
       <c r="J135" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K135" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" ht="12.8">
       <c r="D136" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" ht="12.8">
       <c r="B138" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" ht="12.8">
       <c r="A140" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H141" s="1" t="n">
+    <row r="141" ht="12.8">
+      <c r="H141" s="1">
         <v>20</v>
       </c>
       <c r="I141" s="1" t="s">
@@ -1461,19 +1608,22 @@
       <c r="J141" s="4" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K141" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="142" ht="12.8">
       <c r="B142" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" ht="12.8">
       <c r="A144" s="1" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H145" s="1" t="n">
+    <row r="145" ht="12.8">
+      <c r="H145" s="1">
         <v>21</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -1482,17 +1632,20 @@
       <c r="J145" s="4" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K145" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="146" ht="12.8">
       <c r="B146" s="1" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
